--- a/SEM 3/Progress.xlsx
+++ b/SEM 3/Progress.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Degree\SEM 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2AE4FE-C862-4532-8F22-3AE6F80EC597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28003FC-7D15-4F2E-9034-1CE8BF0C7E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -475,14 +475,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="8" width="15.77734375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="8" width="15.7109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="22.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
@@ -502,7 +502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -525,7 +525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -548,7 +548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
@@ -571,7 +571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
@@ -594,7 +594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
@@ -617,7 +617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
@@ -640,7 +640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
@@ -663,7 +663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -686,7 +686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
@@ -709,7 +709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
@@ -732,10 +732,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
     </row>
-    <row r="15" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>10</v>
       </c>
@@ -758,7 +758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
